--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6600NC_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6600NC_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,250 +544,245 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSW3_CSANG@LEG3</t>
+          <t>FSW3_MINR@LEG3</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSW3_MINR@LEG3</t>
+          <t>FSW3_THDL@LEG3</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSW3_THDL@LEG3</t>
+          <t>FSW3_RELANG@LEG3</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>FSW3_RELANG@LEG3</t>
+          <t>FSW3_RELR@LEG3</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSW3_RELR@LEG3</t>
+          <t>FSW3_STEMR@LEG3</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>FSW3_STEMR@LEG3</t>
+          <t>FSW3_HEADL@LEG3</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>FSW3_HEADL@LEG3</t>
+          <t>NUTHEX3@NUTHEX3</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>NUTHEX3@NUTHEX3</t>
+          <t>DEPTH@NUTCUT3</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT3</t>
+          <t>FSW3_CBR@LEG3</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>FSW3_CBR@LEG3</t>
+          <t>FSW3_CBD@LEG3</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>FSW3_CBD@LEG3</t>
+          <t>D1@BORE1</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>D1@BORE1</t>
+          <t>DEPTH@BORECUT1</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT1</t>
+          <t>D2@BORE2</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>D2@BORE2</t>
+          <t>DEPTH@BORECUT2</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT2</t>
+          <t>D3@BORE3</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>D3@BORE3</t>
+          <t>DEPTH@BORECUT3</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT3</t>
+          <t>THDDIA@THD_End1</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>THDDIA@THD_End1</t>
+          <t>THDPITCH@THD_End1</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1</t>
+          <t>DEPTH@THD_End1</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>DEPTH@THD_End1</t>
+          <t>Profile_Height@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>Profile_Height@THD_End1_PROF</t>
+          <t>Profile_Land@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>Profile_Land@THD_End1_PROF</t>
+          <t>THDPITCH@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1_PROF</t>
+          <t>THDDIA@THD_End2</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>THDDIA@THD_End2</t>
+          <t>THDPITCH@THD_End2</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End2</t>
+          <t>DEPTH@THD_End2</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>DEPTH@THD_End2</t>
+          <t>Profile_Height@THD_End2_PROF</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>Profile_Height@THD_End2_PROF</t>
+          <t>Profile_Land@THD_End2_PROF</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>Profile_Land@THD_End2_PROF</t>
+          <t>THDPITCH@THD_End2_PROF</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End2_PROF</t>
+          <t>HELIXDIA@HELIXSK_3</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_3</t>
+          <t>HEIGHT@HELIX_3</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_3</t>
+          <t>PITCH@HELIX_3</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_3</t>
+          <t>PROF_R@THDPROF_3</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_3</t>
+          <t>APEXR@THDPROF_3</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_3</t>
+          <t>PROF_AX@THDPROF_3</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_3</t>
+          <t>HEXAF@RUN</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>HEXAF@RUN</t>
+          <t>HEXL1@RUN_BODY</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>HEXL1@RUN_BODY</t>
+          <t>HEXL2@RUN_BODY</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>HEXL2@RUN_BODY</t>
+          <t>HEXAF@HEX3</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX3</t>
+          <t>HEXL@HEX3_BODY</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>HEXL@HEX3_BODY</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@End1_Thread</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>$PRP@End1_Thread</t>
+          <t>$PRP@End2_Thread</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>$PRP@End2_Thread</t>
+          <t>$PRP@End3_Thread</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>$PRP@End3_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -875,138 +870,140 @@
         <v>0.571</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>0.54864</v>
       </c>
       <c r="AB2" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.391</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.09728</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.54864</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0.45364</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BG2" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="BH2" t="n">
         <v>2.391</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1.1875</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.60775</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.04511</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.02083</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.1875</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.60775</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.04511</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.02083</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.09728</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.5356</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.54864</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.59375</v>
-      </c>
       <c r="BI2" t="n">
-        <v>2.391</v>
+        <v>1.19</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="BK2" t="n">
         <v>0.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>1.19</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BN2" t="n">
         <v>0.7</v>
       </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>FS6600-12-12-12-FG</t>
+        </is>
+      </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>FS6600-12-12-12-FG</t>
+          <t>ORFS Swivel Branch Tee (male face seal run x female face-seal swivel branch) - face-seal legs with the flats = the thread major (no step), swivel nut mouth counterbored (-10 up), 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>ORFS Swivel Branch Tee (male face seal run x female face-seal swivel branch) - face-seal legs with the flats = the thread major (no step), swivel nut mouth counterbored (-10 up), 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6600NC</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>FS6600NC</t>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1016,30 +1013,25 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6600 (s35, double-pass 2026-10-15, parts.air-way.com/api/series/35, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p16 FS6600-12-12-12-FG (ORFS-p016-t03); FORGED part: Air-Way NON-forged row FF6600-12-12-12-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>Air-Way FF6600 (s35, double-pass 2026-10-15, parts.air-way.com/api/series/35, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p16 FS6600-12-12-12-FG (ORFS-p016-t03); FORGED part: Air-Way NON-forged row FF6600-12-12-12-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged FF6600-12-12-12-O = Brennan forged FS6600-12-12-12-FG p16 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6600 is used only where Brennan FS6600-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5628 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 3 hex arm 0.700 barely clears the run bar corner (0.687)</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
-        <is>
-          <t>forged (-FG): Air-Way non-forged FF6600-12-12-12-O = Brennan forged FS6600-12-12-12-FG p16 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6600 is used only where Brennan FS6600-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5628 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 3 hex arm 0.700 barely clears the run bar corner (0.687)</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
         <is>
           <t>FS6600-12-12-12-FG</t>
         </is>
